--- a/output/sample_informatica_mapping.xlsx
+++ b/output/sample_informatica_mapping.xlsx
@@ -148,7 +148,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3248025" cy="4676775"/>
+    <ext cx="3248025" cy="2619375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
